--- a/src/rag_results_vanilla.xlsx
+++ b/src/rag_results_vanilla.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N167"/>
+  <dimension ref="A1:N250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8631,6 +8631,4047 @@
       </c>
       <c r="N167" s="5" t="n"/>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院醫療保險金、加護病房或燒燙傷病房保險金、祝壽保險金、身故保險金或喪葬費用保險金，以及所繳保險費的退還。
+條文依據：  
+- 摘要</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | summary | 第五條 保險範圍 | 第二條 名詞定義 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="n"/>
+      <c r="K168" s="5" t="n"/>
+      <c r="L168" s="5" t="n"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:47:44</t>
+        </is>
+      </c>
+      <c r="N168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>住院日數計算有什麼特殊規則？</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院日數的計算規則如下：  
+1. 住院日數是按被保險人同一次住院的實際全日住進急性病房或慢性病房（含加護病房及燒燙傷病房）的住院日數計算，包含住院及出院當日。  
+2. 若被保險人出院後又於同一日入院診療，該日不得重複計入住院日數。  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十二條 住院醫療保險金的給付 | 第二條 名詞定義 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="n"/>
+      <c r="K169" s="5" t="n"/>
+      <c r="L169" s="5" t="n"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:47:47</t>
+        </is>
+      </c>
+      <c r="N169" s="5" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>住院醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院醫療保險金的給付規定如下：  
+被保險人於本契約有效期間內因疾病或傷害而住院治療時，本公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以住院日數，給付「住院醫療保險金」。同一保單年度內，同一次住院的住院日數給付上限為三百六十五日。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十四條 醫療保險金給付總額之上限 | 第二十八條 住院醫療保險金日額之減少</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="n"/>
+      <c r="K170" s="5" t="n"/>
+      <c r="L170" s="5" t="n"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:47:49</t>
+        </is>
+      </c>
+      <c r="N170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>加護病房或燒燙傷病房保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+加護病房或燒燙傷病房保險金的給付規定如下：  
+被保險人於契約有效期間內因疾病或傷害住院，並接受加護病房或燒燙傷病房治療者，除住院醫療保險金外，保險公司將依保險單所記載的「住院醫療保險金日額」，乘以入院日當年度的「增額係數」，再乘以實際住進加護病房或燒燙傷病房的日數（含轉入及轉出當日）的二倍，給付「加護病房或燒燙傷病房保險金」。  
+同一保單年度內，同一次住院的加護病房及燒燙傷病房住院日數合計給付上限為365日，但同一日內僅能就其中一種病房給付保險金。
+條文依據：  
+- [第十三條 加護病房或燒燙傷病房保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二十三條 醫療保險金的申領 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="n"/>
+      <c r="K171" s="5" t="n"/>
+      <c r="L171" s="5" t="n"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:47:52</t>
+        </is>
+      </c>
+      <c r="N171" s="5" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載之「住院醫療保險金日額」的二千五百倍，且僅限於本契約有效期間內依第十二條至第十三條所給付之各項保險金的累計總額。
+條文依據：  
+- 第十四條 醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 醫療保險金給付總額之上限 | 第十二條 住院醫療保險金的給付 | 第五條 保險範圍 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="n"/>
+      <c r="K172" s="5" t="n"/>
+      <c r="L172" s="5" t="n"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:47:54</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的給付規定為何?</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的給付規定如下：被保險人於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存時，本公司按「當年度保險金額」給付「祝壽保險金」。
+條文依據：  
+- [第十五條 祝壽保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十四條 祝壽保險金的申領 | payout_items | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="n"/>
+      <c r="K173" s="5" t="n"/>
+      <c r="L173" s="5" t="n"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:47:56</t>
+        </is>
+      </c>
+      <c r="N173" s="5" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>有效期間內身故，保險金如何給付?</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於本契約有效期間內身故時，本公司按「當年度保險金額」給付「身故保險金」。若被保險人於繳費期間內身故，當期已繳付之未到期保險費不予退還，亦不併入身故保險金內給付。若被保險人於有效期間內且實際年齡未滿十五足歲身故，本公司則按「所繳保險費」退還要保人，不適用前述約定。此外，若被保險人為受監護宣告尚未撤銷者，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不負給付責任。  
+條文依據：  
+- [第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第五條 保險範圍 | 第二十二條 失蹤處理 | 第十五條 祝壽保險金的給付</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="n"/>
+      <c r="K174" s="5" t="n"/>
+      <c r="L174" s="5" t="n"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:47:59</t>
+        </is>
+      </c>
+      <c r="N174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>健康促進保險費折減規定</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+健康促進保險費折減規定如下：  
+1. 被保險人需年滿20歲（含）以上，並使用保險公司指定程式加入健康計劃。  
+2. 若於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級），次一保險單年度的保險費可折減：  
+   - 進階會員：折減比例為2%。  
+   - 菁英會員或更高等級：折減比例為3%。  
+3. 折減僅適用於主契約保險費，不包含其他附約、附加條款或批註條款。  
+4. 豁免或復效的保險費不適用折減規定。  
+5. 被保險人需完成程式註冊並授權保險公司取得健康促進相關電子紀錄，保險公司將依紀錄計算會員等級。
+條文依據：  
+- [第十七條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 健康促進保險費折減 | 第二十八條 住院醫療保險金日額之減少 | 第三十條 投保年齡的計算及錯誤的處理 | 第二條 名詞定義 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J175" s="5" t="n"/>
+      <c r="K175" s="5" t="n"/>
+      <c r="L175" s="5" t="n"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:03</t>
+        </is>
+      </c>
+      <c r="N175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>除外責任的解釋?</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+除外責任是指保險公司不負給付保險金責任的情形，包含被保險人因故意行為、犯罪行為、非法施用毒品等原因所致疾病或傷害，以及因美容手術、健康檢查、懷孕、流產或分娩等特定事故住院診療的情況。但部分情形有例外，例如重建基本功能的必要整型手術、特定懷孕相關疾病、醫療行為必要的流產或剖腹產等，保險公司仍負給付責任。  
+條文依據：  
+- [第十八條 除外責任（一）]  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十九條 除外責任（二） | 第八條 告知義務與本契約的解除 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="n"/>
+      <c r="K176" s="5" t="n"/>
+      <c r="L176" s="5" t="n"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:06</t>
+        </is>
+      </c>
+      <c r="N176" s="5" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>哪些疾病被含在除外責任?</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+以下疾病被列為除外責任，保險公司不負給付第十二條至第十三條保險金的責任：  
+1. 美容手術、外科整型（但為重建基本功能所作之必要整型不在此限）。  
+2. 外觀可見之天生畸形。  
+3. 健康檢查、療養、靜養、戒毒、戒酒、護理或養老之非以直接診治病人為目的者。  
+4. 懷孕、流產或分娩及其併發症（但特定懷孕相關疾病、醫療行為必要之流產及剖腹產不在此限）。  
+5. 不孕症、人工受孕或非以治療為目的之避孕及絕育手術。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J177" s="5" t="n"/>
+      <c r="K177" s="5" t="n"/>
+      <c r="L177" s="5" t="n"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:09</t>
+        </is>
+      </c>
+      <c r="N177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>進行美容手術住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因美容手術住院診療者，本公司不負給付保險金的責任。但若美容手術是為重建基本功能所作之必要整型，則不在此限，可以申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="n"/>
+      <c r="K178" s="5" t="n"/>
+      <c r="L178" s="5" t="n"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:10</t>
+        </is>
+      </c>
+      <c r="N178" s="5" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>因胎兒染色體異常進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠。根據條款，被保險人因「胎兒染色體異常之手術」住院診療，不屬於除外責任範圍，因此本公司負有給付保險金的責任。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="n"/>
+      <c r="K179" s="5" t="n"/>
+      <c r="L179" s="5" t="n"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:15</t>
+        </is>
+      </c>
+      <c r="N179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>因胎位不正進行手術而住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因胎位不正進行手術而住院屬於除外責任範圍，保險公司不負給付保險金的責任。然而，若手術屬於「醫療行為必要之剖腹產」且符合胎位不正的條件，則不在除外責任範圍內，可申請理賠。
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | 第二條 名詞定義 | payout_items | 第十三條 加護病房或燒燙傷病房保險金的給付</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J180" s="5" t="n"/>
+      <c r="K180" s="5" t="n"/>
+      <c r="L180" s="5" t="n"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:19</t>
+        </is>
+      </c>
+      <c r="N180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>因自殺未遂導致住院可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，因被保險人故意行為（包括自殺及自殺未遂）所致之住院診療，本公司不負給付第十二條至第十三條保險金的責任。  
+條文依據：  
+- [第十八條 除外責任（一）]</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十八條 除外責任（一） | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items | 第十條 契約的終止（二）</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="n"/>
+      <c r="K181" s="5" t="n"/>
+      <c r="L181" s="5" t="n"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:20</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>被保險人在投保一年內故意自殺者，可以申請理賠嗎?</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人在投保一年內故意自殺者，依條款規定，本公司不負給付身故保險金或喪葬費用保險金的責任。但若故意自殺發生於契約訂立或復效之日起二年後，本公司仍負給付責任。
+條文依據：  
+- [第十九條 除外責任（二）]</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 除外責任（二） | 第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十條 契約的終止（二） | 第三十條 投保年齡的計算及錯誤的處理 | 第十八條 除外責任（一）</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="n"/>
+      <c r="K182" s="5" t="n"/>
+      <c r="L182" s="5" t="n"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:22</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>申請理賠有什麼時間規定嗎?</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請理賠的時間規定如下：要保人、被保險人或受益人應於知悉本公司應負保險責任之事故後十日內通知本公司，並於通知後儘速檢具所需文件向本公司申請給付保險金。本公司應於收齊前項文件後十五日內給付保險金。但若因可歸責於本公司之事由未能在約定期限內給付，則應按年利一分加計利息給付。
+條文依據：  
+- [第二十一條 保險事故的通知與保險金的申請時間]</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>第二十一條 保險事故的通知與保險金的申請時間 | 第六條 第二期以後保險費的交付、寬限期間及契約效力的停止 | 第七條 本契約效力的恢復 | 第三條 契約撤銷權 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="n"/>
+      <c r="K183" s="5" t="n"/>
+      <c r="L183" s="5" t="n"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:24</t>
+        </is>
+      </c>
+      <c r="N183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>燒燙傷病房保險金怎麼申領?</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申領燒燙傷病房保險金時，受益人需依第十二條至第十三條約定，檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 醫療診斷書或住院證明，並列明進、出燒燙傷病房的日期。（但要保人或被保險人為醫師時，不得為被保險人出具診斷書或住院證明。）  
+4. 受益人的身分證明。  
+此外，本公司基於審核保險金之需要，得徵詢其他醫師的醫學專業意見，並經受益人同意調閱被保險人之就醫相關資料，相關費用由本公司負擔。
+條文依據：  
+- [第二十三條 醫療保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 醫療保險金的申領 | 第十三條 加護病房或燒燙傷病房保險金的給付 | payout_items | 第二條 名詞定義 | 第二十一條 保險事故的通知與保險金的申請時間</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="n"/>
+      <c r="K184" s="5" t="n"/>
+      <c r="L184" s="5" t="n"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:27</t>
+        </is>
+      </c>
+      <c r="N184" s="5" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>活到99歲怎麼申請祝壽金?</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+申請祝壽保險金時，受益人需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 受益人的身分證明。  
+條文依據：  
+- [第二十四條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 祝壽保險金的給付 | 第二十四條 祝壽保險金的申領 | 第五條 保險範圍 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | announcement_history</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="n"/>
+      <c r="K185" s="5" t="n"/>
+      <c r="L185" s="5" t="n"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:29</t>
+        </is>
+      </c>
+      <c r="N185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>被保人身故怎麼申請理賠</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+受益人申領「身故保險金」或「喪葬費用保險金」時，需檢具以下文件：  
+1. 保險單或其謄本。  
+2. 保險金申請書。  
+3. 被保險人死亡證明書及除戶戶籍謄本。  
+4. 受益人的身分證明。  
+條文依據：  
+- [第二十五條 身故保險金或喪葬費用保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 所繳保險費的退還、身故保險金或喪葬費用保險金的給付 | 第十二條至第十三條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十二條 失蹤處理 | 第二十五條 身故保險金或喪葬費用保險金的申領 | 第十九條 除外責任（二）</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J186" s="5" t="n"/>
+      <c r="K186" s="5" t="n"/>
+      <c r="L186" s="5" t="n"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:32</t>
+        </is>
+      </c>
+      <c r="N186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>投保15年後，因手術住院3天，住院日額為2500元，請問可以申請多少理賠?</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據第十二條，住院醫療保險金的計算方式為「住院醫療保險金日額」乘以住院日數，再乘以入院日當年度之「增額係數」。若住院日額為2500元，住院3天，且未提供增額係數的具體數值，則理賠金額暫以以下公式計算：  
+2500元 × 3天 × 增額係數。  
+由於增額係數未明確提供，無法得出確切理賠金額。  
+條文依據：  
+- [第十二條 住院醫療保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 住院醫療保險金的給付 | 第十三條 加護病房或燒燙傷病房保險金的給付 | 第二十八條 住院醫療保險金日額之減少 | 第十一條 住院次數之計算及契約有效期間屆滿後住院之處理 | payout_items</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="n"/>
+      <c r="K187" s="5" t="n"/>
+      <c r="L187" s="5" t="n"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:35</t>
+        </is>
+      </c>
+      <c r="N187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：住院手術醫療保險金、門診手術醫療保險金、特定處置保險金、意外創傷縫合處置保險金、意外住院手術醫療保險金、祝壽保險金、所繳保險費的退還、身故保險金或喪葬費用保險金。
+條文依據：  
+- [第五條 保險範圍]  
+- [給付項目]</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | summary | 第四條 名詞定義 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="n"/>
+      <c r="K188" s="5" t="n"/>
+      <c r="L188" s="5" t="n"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:39</t>
+        </is>
+      </c>
+      <c r="N188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>保險金額是否有上限?</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保險金額有上限。本契約有效期間內，依第十一條至第十五條所給付之各項保險金，其累計給付總額上限為保險單上所記載「保險金額」的一千五百倍。  
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第三十條 保險金額之減少 | 第五條 保險範圍 | 第十九條 健康促進保險費折減 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="n"/>
+      <c r="K189" s="5" t="n"/>
+      <c r="L189" s="5" t="n"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:41</t>
+        </is>
+      </c>
+      <c r="N189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>投保後5天發生手術，是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據提供的條款內容，無法判斷是否有等待期間的規定，因此無法確定投保後5天發生手術是否符合理賠條件。  
+條文依據：  
+找不到相關內容</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="n"/>
+      <c r="K190" s="5" t="n"/>
+      <c r="L190" s="5" t="n"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:43</t>
+        </is>
+      </c>
+      <c r="N190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內因疾病或傷害，經醫師診斷必須於醫院住院接受附表一所列的手術治療且已實際接受手術者，本公司依保險單記載的「保險金額」乘以手術日當年度的「增額係數」，再乘以手術給付倍數，給付住院手術醫療保險金。  
+2. 同一次手術中，若於同一手術位置接受二項以上手術項目，僅給付手術給付倍數最高的手術項目。  
+3. 未載明於附表一的手術項目，將與被保險人協議比照附表內程度相當的手術項目，決定給付倍數。  
+4. 以下情形不負給付責任：  
+   - 依據契約除外責任條款規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十一條 住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 第十二條 門診手術醫療保險金 | payout_items | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J191" s="5" t="n"/>
+      <c r="K191" s="5" t="n"/>
+      <c r="L191" s="5" t="n"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:46</t>
+        </is>
+      </c>
+      <c r="N191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>門診手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+門診手術醫療保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所門診接受附表一的手術治療且已實際接受手術者，本公司按保險單上所記載之「保險金額」乘以手術日當年度之「增額係數」，再乘以手術給付倍數，給付「門診手術醫療保險金」。  
+2. 同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付手術給付倍數最高的手術項目。  
+3. 同一保險單年度內，門診手術醫療保險金的給付以十次為限。  
+4. 未載明於附表一所列的手術項目，本公司將與被保險人協議比照該表內之手術項目，決定給付倍數。  
+5. 以下情形不負給付責任：  
+   - 依據本契約除外責任條款的規定不在給付範圍內。  
+   - 不屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。  
+條文依據：  
+- [第十二條 門診手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第十一條 住院手術醫療保險金 | payout_items | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="n"/>
+      <c r="K192" s="5" t="n"/>
+      <c r="L192" s="5" t="n"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:49</t>
+        </is>
+      </c>
+      <c r="N192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>意外住院手術醫療保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外住院手術醫療保險金的給付規定如下：  
+1. 被保險人於契約有效期間內且保險年齡未滿七十歲，因傷害經醫師診斷在住院期間必須接受手術治療且已接受手術者，本公司按保險單所記載之「保險金額」的三倍，乘以手術日當年度之「增額係數」，給付「意外住院手術醫療保險金」。  
+2. 若被保險人於同一次手術中，於同一手術位置接受二項以上手術項目時，僅給付一次「意外住院手術醫療保險金」。
+條文依據：  
+- [第十三條 意外住院手術醫療保險金]</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外住院手術醫療保險金 | 第十一條 住院手術醫療保險金 | 第十五條 意外創傷縫合處置保險金 | 第二十條 除外責任（一） | 第十二條 門診手術醫療保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J193" s="5" t="n"/>
+      <c r="K193" s="5" t="n"/>
+      <c r="L193" s="5" t="n"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:52</t>
+        </is>
+      </c>
+      <c r="N193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>特定處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+特定處置保險金的給付規定如下：  
+1. 被保險人因疾病或傷害，經醫師診斷必須於醫院或診所接受附表二所列之特定處置治療且已接受處置者，保險公司將依保險單記載的「保險金額」，乘以特定處置日當年度的「增額係數」，再乘以特定處置給付倍數，給付「特定處置保險金」。  
+2. 同一次處置治療中，若於同一治療位置接受二項以上特定處置項目，僅給付特定處置給付倍數最高的特定處置項目。  
+3. 若被保險人接受的處置未載明於附表二所列之特定處置項目，保險公司不負給付特定處置保險金的責任。  
+4. 同一保險單年度的「特定處置保險金」給付次數以十次為限。
+條文依據：  
+- [第十四條 特定處置保險金]</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 特定處置保險金 | 第十五條 意外創傷縫合處置保險金 | 附表二：特定處置項目及給付倍數表 | 第五條 保險範圍 | 附表三：意外創傷縫合處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="n"/>
+      <c r="K194" s="5" t="n"/>
+      <c r="L194" s="5" t="n"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:55</t>
+        </is>
+      </c>
+      <c r="N194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付規定</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付規定如下：  
+1. 被保險人因意外傷害事故，於醫院或診所接受附表三所列的意外創傷縫合處置治療者，本公司將依保險單記載的「保險金額」，乘以當年度的「增額係數」及「意外創傷縫合處置給付倍數」計算給付金額。  
+2. 同一次意外傷害事故，僅就傷口最大者給付保險金，且以給付一次為限。  
+3. 若被保險人因同一意外傷害事故已申領「住院手術醫療保險金」或「門診手術醫療保險金」，則不再給付「意外創傷縫合處置保險金」。  
+條文依據：  
+- [第十五條 意外創傷縫合處置保險金]</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 意外創傷縫合處置保險金 | 附表三：意外創傷縫合處置項目及給付倍數表 | 第十四條 特定處置保險金 | 第二十條 除外責任（一） | 第十三條 意外住院手術醫療保險金 | 附表二：特定處置項目及給付倍數表</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J195" s="5" t="n"/>
+      <c r="K195" s="5" t="n"/>
+      <c r="L195" s="5" t="n"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:57</t>
+        </is>
+      </c>
+      <c r="N195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>醫療保險金給付總額之上限</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+醫療保險金給付總額之上限為保險單上所記載的「保險金額」之一千五百倍，且不包含其他附約、附加條款及批註條款。  
+條文依據：  
+- [第十六條 醫療保險金給付總額之上限]</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 醫療保險金給付總額之上限 | 第十二條 門診手術醫療保險金 | 第五條 保險範圍 | 第十一條 住院手術醫療保險金 | 第十三條 意外住院手術醫療保險金 | 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J196" s="5" t="n"/>
+      <c r="K196" s="5" t="n"/>
+      <c r="L196" s="5" t="n"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:48:59</t>
+        </is>
+      </c>
+      <c r="N196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>祝壽保險金的領取規定為何?</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+祝壽保險金的領取規定如下：  
+1. 被保險人需於本契約有效期間且保險年齡到達九十九歲之保險單週年日仍生存，方可申領祝壽保險金。  
+2. 受益人申領祝壽保險金時，需檢具以下文件：  
+   - 保險單或其謄本  
+   - 保險金申請書  
+   - 受益人的身分證明  
+條文依據：  
+- [第十七條 祝壽保險金]  
+- [第二十六條 祝壽保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 祝壽保險金 | 第二十六條 祝壽保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十三條 保險事故的通知與保險金的申請時間 | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J197" s="5" t="n"/>
+      <c r="K197" s="5" t="n"/>
+      <c r="L197" s="5" t="n"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:02</t>
+        </is>
+      </c>
+      <c r="N197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>身故時領取保險金有什麼規則?</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+身故時領取保險金的規則如下：  
+1. 被保險人於本契約有效期間內身故者，本公司按「當年度保險金額」給付「身故保險金」。  
+2. 若被保險人於本契約有效期間且實際年齡未滿十五足歲身故者，本公司退還「所繳保險費」予要保人，不適用「當年度保險金額」的約定。  
+3. 若被保險人於訂立契約時受監護宣告尚未撤銷，其身故保險金變更為喪葬費用保險金，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分本公司不負給付責任，並退還超過部分的已繳保險費。  
+4. 若要保人向多家保險公司投保喪葬費用保險金，且合計金額超過限額，本公司僅依限額比例分擔責任。  
+條文依據：  
+- [第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金]</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金 | 第二十七條 身故保險金或喪葬費用保險金的申領 | 第十一條至第十五條保險金的受益人，為被保險人本人，本公司不受理其指定或變更。 | 第二十一條 除外責任（二） | 第五條 保險範圍</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J198" s="5" t="n"/>
+      <c r="K198" s="5" t="n"/>
+      <c r="L198" s="5" t="n"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:05</t>
+        </is>
+      </c>
+      <c r="N198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>什麼情況下可以保費折減?</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人年齡達20歲（含）以上，並使用保險公司指定程式加入健康計劃，於「指定日期」的會員等級符合進階會員或菁英會員（或更高等級）標準者，可享次一保險單年度的保費折減。折減比例為進階會員2%，菁英會員或更高等級3%。但豁免或復效的保險費不適用折減約定。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十條 保險金額之減少 | 第二十條 除外責任（一） | 第三十一條 投保年齡的計算及錯誤的處理 | 第十八條 所繳保險費的退還、身故保險金或喪葬費用保險金</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J199" s="5" t="n"/>
+      <c r="K199" s="5" t="n"/>
+      <c r="L199" s="5" t="n"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:08</t>
+        </is>
+      </c>
+      <c r="N199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>角膜切除術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+角膜切除術可以申請理賠，根據「手術項目與給付倍數」的規定，角膜切除術（編號1305）屬於手術項目表所列的手術項目，給付倍數為5。
+條文依據：  
+- [附表一：手術項目與給付倍數]</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J200" s="5" t="n"/>
+      <c r="K200" s="5" t="n"/>
+      <c r="L200" s="5" t="n"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:09</t>
+        </is>
+      </c>
+      <c r="N200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>白內障手術是否可以申請理賠?</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+白內障手術是否可以申請理賠需視手術是否符合以下條件：  
+1. 手術項目需列於附表一中，例如「晶體切除術合併玻璃體切除術」（給付倍數30）或其他相關手術。  
+2. 手術需屬全民健康保險醫療服務給付項目及支付標準第二部第二章第七節或第三部第三章第四節第三項所列舉的手術。若不屬於此範圍，則不予理賠。  
+3. 若手術因除外責任條款中的原因（如美容手術或非治療目的）進行，則不予理賠。
+條文依據：  
+- 第十二條 門診手術醫療保險金  
+- 附表一：手術項目與給付倍數</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 門診手術醫療保險金 | 第二十條 除外責任（一） | 附表一：手術項目與給付倍數 | payout_items | 第十一條 住院手術醫療保險金</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J201" s="5" t="n"/>
+      <c r="K201" s="5" t="n"/>
+      <c r="L201" s="5" t="n"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:12</t>
+        </is>
+      </c>
+      <c r="N201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>保障範圍包括哪些項目？</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保障範圍包括：意外事故身故保險金或喪葬費用保險金、意外事故失能保險金、每月生活照護保險金、重大燒燙傷保險金、意外骨折保險金、傷害醫療日額保險金、意外創傷縫合處置保險金。
+條文依據：  
+- [第五條 保險範圍]</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第五條 保險範圍 | 第十五條 每月生活照護保險金的給付 | 第三十條 不保事項 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J202" s="5" t="n"/>
+      <c r="K202" s="5" t="n"/>
+      <c r="L202" s="5" t="n"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:14</t>
+        </is>
+      </c>
+      <c r="N202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>發生意外事故身故，理賠內容為何?</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故身故的理賠內容包括「意外事故身故保險金」或「喪葬費用保險金」。理賠金額依意外傷害事故的種類分為以下兩種：  
+1. 一般意外傷害事故：給付「傷害醫療保險金日額」的五百倍。  
+2. 特定意外傷害事故：給付「傷害醫療保險金日額」的一千倍。  
+此外，若被保險人於意外傷害事故發生後超過一百八十日身故，但受益人能證明身故與該事故具有因果關係者，仍可依上述約定申請理賠。若被保險人受監護宣告尚未撤銷，其理賠內容則變更為「喪葬費用保險金」，且喪葬費用保險金額不得超過遺產稅喪葬費扣除額之半數，超過部分不予理賠。  
+條文依據：  
+- [第十二條 意外事故身故保險金或喪葬費用保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第十四條 保險給付的限制 | payout_items | 第十一條 契約的終止（二） | 第二十一條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J203" s="5" t="n"/>
+      <c r="K203" s="5" t="n"/>
+      <c r="L203" s="5" t="n"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:17</t>
+        </is>
+      </c>
+      <c r="N203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>意外事故失能保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外事故失能保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受意外傷害事故，並於事故發生後180日內致成附表二所列失能程度之一者，本公司依意外傷害事故種類及失能程度，按以下金額給付：  
+   - 一般意外傷害事故：「傷害醫療保險金日額」的500倍乘以附表二給付比例。  
+   - 特定意外傷害事故：「傷害醫療保險金日額」的1000倍乘以附表二給付比例。  
+2. 若超過180日致成失能，受益人能證明失能與事故具有因果關係者，仍可申請保險金，不受180日限制。  
+3. 同一事故致成多項失能時，僅給付同一手或足中較嚴重項目的保險金，且給付金額以事故種類的上限為限。  
+4. 若失能合併以前的失能，僅給付較嚴重項目，但需扣除以前已給付的保險金。  
+條文依據：  
+- [第十三條 意外事故失能保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 意外事故失能保險金的給付 | 第十五條 每月生活照護保險金的給付 | 第十四條 保險給付的限制 | 第十二條 意外事故身故保險金或喪葬費用保險金的給付 | 第二十三條 意外事故失能保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J204" s="5" t="n"/>
+      <c r="K204" s="5" t="n"/>
+      <c r="L204" s="5" t="n"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:21</t>
+        </is>
+      </c>
+      <c r="N204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>每月生活照護保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每月生活照護保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，並於事故發生後一百八十日內致成附表二所列第一級至第六級失能程度之一時，本公司自失能診斷確定當日起，按「傷害醫療保險金日額」的二十倍乘以附表二給付比例所得之金額，按月給付，以十二個月為限。  
+2. 若被保險人於事故發生後超過一百八十日致成失能，受益人需證明失能與事故具有因果關係，本公司仍依上述規定給付，不受一百八十日限制。  
+3. 同一事故若致成多項失能，僅給付較嚴重項目，且最高以「傷害醫療保險金日額」的二十倍為限。  
+4. 累計給付金額最高以「傷害醫療保險金日額」的一千二百倍為限。  
+5. 若被保險人於給付期間內身故，未支領部分將貼現後一次給付予法定繼承人。
+條文依據：  
+- [第十五條 每月生活照護保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>第二十四條 每月生活照護保險金的申領 | 第十五條 每月生活照護保險金的給付 | payout_items | 第十八條 傷害醫療日額保險金的給付 | 第五條 保險範圍 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J205" s="5" t="n"/>
+      <c r="K205" s="5" t="n"/>
+      <c r="L205" s="5" t="n"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:25</t>
+        </is>
+      </c>
+      <c r="N205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>重大燒燙傷保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+重大燒燙傷保險金的給付條件為：被保險人於本契約有效期間內遭受「意外傷害事故」，蒙受燒燙傷之傷害，經診斷符合「重大燒燙傷」者，本公司按「傷害醫療保險金日額」的二百五十倍給付「重大燒燙傷保險金」。此保險金的給付以一次為限。
+條文依據：  
+- [第十六條 重大燒燙傷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 重大燒燙傷保險金的給付 | 第二十五條 重大燒燙傷保險金的申領 | 第五條 保險範圍 | payout_items | 第二十九條 除外責任（原因）</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J206" s="5" t="n"/>
+      <c r="K206" s="5" t="n"/>
+      <c r="L206" s="5" t="n"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:28</t>
+        </is>
+      </c>
+      <c r="N206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>意外骨折保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外骨折保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生之日起一百八十日內，經合格醫院或診所診斷為附表三骨折別表所列骨折項目之一（含不完全骨折及骨骼龜裂），本公司按「傷害醫療保險金日額」的二倍給付意外骨折保險金。  
+2. 若超過一百八十日診斷確定骨折，受益人能證明骨折與事故具有因果關係者，仍可依上述規定給付，不受一百八十日限制。  
+3. 同一意外傷害事故僅給付一次意外骨折保險金。  
+4. 若骨折非屬附表三骨折別表所列項目，需由本公司與被保險人協議核付；但若骨折部位為骨折別表內明訂不給付之部位，則本公司不負給付責任。
+條文依據：  
+- [第十七條 意外骨折保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 意外骨折保險金的給付 | 第十八條 傷害醫療日額保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第十三條 意外事故失能保險金的給付 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J207" s="5" t="n"/>
+      <c r="K207" s="5" t="n"/>
+      <c r="L207" s="5" t="n"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:30</t>
+        </is>
+      </c>
+      <c r="N207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>傷害醫療日額保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+傷害醫療日額保險金的給付條件如下：  
+1. 被保險人於契約有效期間內遭受「意外傷害事故」，自事故發生日起一百八十日內於「醫院」接受住院治療者，本公司按「傷害醫療保險金日額」乘以實際住院日數給付，最高以九十日為限。  
+2. 若治療超過一百八十日，受益人能證明治療與事故具有因果關係者，仍可依上述規定給付，不受一百八十日限制。  
+3. 若因骨折未住院或住院未達附表三骨折別表所訂日數，未住院部分按骨折別表所訂日數乘以「傷害醫療保險金日額」的二分之一給付，合計給付日數以骨折別表所訂日數為上限。  
+4. 骨折給付依骨骼損傷程度區分：完全骨折按日數全額給付、不完全骨折按日數二分之一給付、骨骼龜裂按日數四分之一給付。同時發生多項骨折時，僅給付較高等級的保險金。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第二十七條 傷害醫療日額保險金的申領 | 第十五條 每月生活照護保險金的給付 | 第三十四條 傷害醫療保險金日額之減少 | 第十九條 意外創傷縫合處置保險金的給付 | 附表二：失能程度與保險金給付表 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="n"/>
+      <c r="K208" s="5" t="n"/>
+      <c r="L208" s="5" t="n"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:35</t>
+        </is>
+      </c>
+      <c r="N208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>意外創傷縫合處置保險金的給付為何?</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+意外創傷縫合處置保險金的給付條件為：被保險人於本契約有效期間內遭受「意外傷害事故」，並於「醫院」或「診所」經醫師診斷必須接受創傷縫合處置治療且已接受縫合處置者，本公司按「傷害醫療保險金日額」給付「意外創傷縫合處置保險金」。同一意外傷害事故僅給付一次。
+條文依據：  
+- [第十九條 意外創傷縫合處置保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 意外創傷縫合處置保險金的給付 | 第二十八條 意外創傷縫合處置保險金的申領 | 第五條 保險範圍 | 第十七條 意外骨折保險金的給付 | payout_items | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J209" s="5" t="n"/>
+      <c r="K209" s="5" t="n"/>
+      <c r="L209" s="5" t="n"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:38</t>
+        </is>
+      </c>
+      <c r="N209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>因意外導致視力衰退，是否能申請理賠?</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+因意外導致視力衰退，若符合「失明」的定義，即視力永久在萬國式視力表0.02以下，或包括眼球喪失、摘出、僅能辨明暗或辨眼前一公尺以內手動或辨眼前五公分以內指數者，則可申請理賠。此外，視力障害的測定需經過六個月的治療判定，但若屬眼球摘出等明顯無法復原的情況，則不受此限制。  
+條文依據：  
+- [註2]</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>第二十三條 意外事故失能保險金的申領 | 第十三條 意外事故失能保險金的給付 | 註2： | 第三十條 不保事項 | 第二十六條 意外骨折保險金的申領 | 附表二：失能程度與保險金給付表</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J210" s="5" t="n"/>
+      <c r="K210" s="5" t="n"/>
+      <c r="L210" s="5" t="n"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:40</t>
+        </is>
+      </c>
+      <c r="N210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>GI1</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>肋骨骨折是否可以申請理賠?理賠金額為多少?</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+肋骨骨折可以申請理賠，理賠金額依附表三骨折別表所訂完全骨折日數為20天計算。若肋骨骨折屬完全骨折，則理賠金額為「傷害醫療保險金日額」乘以20天；若屬不完全骨折，則按完全骨折日數的二分之一（10天）計算；若屬骨骼龜裂，則按完全骨折日數的四分之一（5天）計算。
+條文依據：  
+- [第十八條 傷害醫療日額保險金的給付]  
+- [附表三：骨折別表]</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>第十八條 傷害醫療日額保險金的給付 | 第十七條 意外骨折保險金的給付 | 第二十六條 意外骨折保險金的申領 | 第三十條 不保事項 | 第五條 保險範圍 | 附表三：骨折別表</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J211" s="5" t="n"/>
+      <c r="K211" s="5" t="n"/>
+      <c r="L211" s="5" t="n"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:42</t>
+        </is>
+      </c>
+      <c r="N211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，假設投保保額為100萬元，於第二保單年度接受「移植器官」，這樣可以領多少保險金?</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度（含）以後的有效期間內，初次診斷確定罹患「特定重大傷病」並接受「移植器官」，可獲得「特定重大傷病保險金」，其金額為保險金額的20%。假設投保保額為100萬元，則可領取20萬元的「特定重大傷病保險金」。  
+條文依據：  
+- [第十三條 特定重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>第十五條 滿期保險金的給付 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目 | 第十三條 特定重大傷病保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J212" s="5" t="n"/>
+      <c r="K212" s="5" t="n"/>
+      <c r="L212" s="5" t="n"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:45</t>
+        </is>
+      </c>
+      <c r="N212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，若要理賠重大傷病保險金，一定要檢附全民健保開立的重大傷病證明才能拿到保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不一定需要檢附全民健保開立的重大傷病證明。若被保險人的「重大傷病」係由診治醫師逕行認定，並已取得一家「區域醫院」層級以上（含）之醫療院所開立且符合投保當時「重大傷病範圍」的診斷書及當次「重大傷病」病歷摘要，則可免向全民健康保險保險人申請，並以該診斷書及病歷摘要替代重大傷病證明文件。  
+條文依據：  
+- [第二十二條 重大傷病保險金、特定重大傷病保險金的申領]</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | other_metadata | 第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J213" s="5" t="n"/>
+      <c r="K213" s="5" t="n"/>
+      <c r="L213" s="5" t="n"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:49</t>
+        </is>
+      </c>
+      <c r="N213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>一定要有健保身分才能申請重大傷病理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，被保險人若喪失全民健康保險被保險人資格，需先申請加保全民健康保險後，才能申領重大傷病保險金。然而，若被保險人因意外傷害事故罹患重大傷病，則不受此限制。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 第十二條 重大傷病保險金的給付 | other_metadata | 第三十條 不保事項 | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J214" s="5" t="n"/>
+      <c r="K214" s="5" t="n"/>
+      <c r="L214" s="5" t="n"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:52</t>
+        </is>
+      </c>
+      <c r="N214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>重大傷病的項目如果在投保後有新增，可以從優申請理賠嗎？</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以申請理賠，但需符合以下條件：重大傷病項目若在投保後新增，理賠範圍以「訂立時」及「有效期間內被保險人診斷確定當時」由中央衛生主管機關公告之最新項目為準。因此，只要新增的重大傷病項目在被保險人診斷確定時已被公告為有效項目，即可申請理賠。
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第二條 名詞定義 | payout_items</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J215" s="5" t="n"/>
+      <c r="K215" s="5" t="n"/>
+      <c r="L215" s="5" t="n"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:55</t>
+        </is>
+      </c>
+      <c r="N215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>我的保單之前有停效，在復效後五天被診斷出重大疾病是否可申請理賠？</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+依據條款，復效後所發生的疾病需符合等待期間的規定才能申請理賠。根據第二條名詞定義，等待期間指自復效日起持續有效三十日之期間，若屬附表一所載「需積極或長期治療之癌症」，則等待期間為九十日。因此，復效後五天被診斷出的重大疾病不符合等待期間的規定，無法申請理賠。
+條文依據：  
+- [第二條 名詞定義]  
+- [第八條 本契約效力的恢復]</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>第八條 本契約效力的恢復 | 第三十條 不保事項 | 第五條 保險範圍 | other_metadata | 第二條 名詞定義 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J216" s="5" t="n"/>
+      <c r="K216" s="5" t="n"/>
+      <c r="L216" s="5" t="n"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:57</t>
+        </is>
+      </c>
+      <c r="N216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>領完重大傷病保險金，主約終止後，附約可以繼續有效嗎?</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以。根據條文規定，若主約因重大傷病診斷確定而終止時，要保人於附約的有效期間內，仍可繼續繳交附約保險費，以延續附約效力。
+條文依據：  
+- [第十一條 契約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 契約的終止（二） | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 第五條 保險範圍 | payout_items | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J217" s="5" t="n"/>
+      <c r="K217" s="5" t="n"/>
+      <c r="L217" s="5" t="n"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:49:59</t>
+        </is>
+      </c>
+      <c r="N217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Q1：因為慢性精神病的保險給付僅有保額的20%，我可以先不申請給付，等之後發生其他重大傷病後，再申請重大傷病保險金嗎?Q2：但如果我不申請，保險公司不會知道我有罹患慢性精神病阿，所以我就可以領之後的重大傷病100%保額嗎?</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+Q1：根據條款，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使您選擇不申請慢性精神病的保險給付，未來若罹患其他重大傷病，保險公司仍僅會給付其中一項的「重大傷病保險金」，並不會因未申請慢性精神病而改變給付比例。  
+Q2：條款未提及保險公司是否會因未申請慢性精神病保險金而不知情，但條款明確規定「重大傷病保險金」的給付僅限一項，且慢性精神病的給付比例為保額的20%。因此，即使未申請慢性精神病的保險金，未來罹患其他重大傷病時，保險公司仍會依條款規定進行審核與給付，並不會因未申請而自動給付100%保額。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 第十三條 特定重大傷病保險金的給付 | 第三十條 不保事項 | 第二十八條 除外責任（一） | 第二十二條 重大傷病保險金、特定重大傷病保險金的申領 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J218" s="5" t="n"/>
+      <c r="K218" s="5" t="n"/>
+      <c r="L218" s="5" t="n"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:13</t>
+        </is>
+      </c>
+      <c r="N218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>失智症會賠嗎？賠多少？</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+失智症是否賠付及賠付金額需視其是否符合「重大傷病」的範圍。根據條款，若失智症屬於附表一所列「重大傷病」範圍，且被保險人於等待期間屆滿翌日或契約復效日起的有效期間內，經醫院醫師初次診斷確定罹患，並取得符合規定的重大傷病證明或診斷書，則可依保險單年度計算方式給付「重大傷病保險金」。賠付金額依以下方式計算：  
+1. 第一保險單年度：「年繳應繳保險費總額」的一點零五倍。  
+2. 第二保險單年度（含）以後：  
+   - 若屬附表一所載「六、慢性精神病」：「保險金額的百分之二十」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+   - 若屬其他「重大傷病範圍」項目：「保險金額」或「年繳應繳保險費總額」的一點零五倍，二者取其大者。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [附表一：全民健康保險重大傷病項目]</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>第十七條 完全失能保險金的給付 | 第二十九條 除外責任（二） | payout_items | 第十二條 重大傷病保險金的給付 | 第三十條 不保事項 | 附表二：完全失能程度表 | 附表一：全民健康保險重大傷病項目</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J219" s="5" t="n"/>
+      <c r="K219" s="5" t="n"/>
+      <c r="L219" s="5" t="n"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:18</t>
+        </is>
+      </c>
+      <c r="N219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>投保新鍾心滿福後，於第二保單年度罹患子宮頸惡性腫瘤，且已給付重大傷病保險金。第五保單年度時又罹患慢性腎衰竭，這樣還可以申領重大傷病保險金的給付嗎?</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不可以再次申領重大傷病保險金。根據條款規定，被保險人同時或先後罹患二項以上「重大傷病」時，本公司僅給付一項「重大傷病保險金」。因此，即使於第五保單年度罹患慢性腎衰竭，因已於第二保單年度因子宮頸惡性腫瘤申領過重大傷病保險金，無法再次申領。
+條文依據：  
+- [第十二條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十二條 重大傷病保險金的給付 | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="n"/>
+      <c r="K220" s="5" t="n"/>
+      <c r="L220" s="5" t="n"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:21</t>
+        </is>
+      </c>
+      <c r="N220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ZCN</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>12歲的被保險人可以有健康促進保險費折減嗎？</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+12歲的被保險人無法享有健康促進保險費折減，因為第十九條明確規定，只有實際年齡達十八歲（含）以上的被保險人才符合折減資格。
+條文依據：  
+- [第十九條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>第十九條 健康促進保險費折減 | 第三十八條 投保年齡的計算及錯誤的處理 | 第三十四條 減額繳清保險 | 第二條 名詞定義 | 第十六條 所繳保險費加計利息的退還、身故保險金或喪葬費用保險金的給付 | 附表二：完全失能程度表</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J221" s="5" t="n"/>
+      <c r="K221" s="5" t="n"/>
+      <c r="L221" s="5" t="n"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:24</t>
+        </is>
+      </c>
+      <c r="N221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ZDN</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於投保鍾心滿溢後的第10天就罹患慢性腎衰竭，請問可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，若被保險人於等待期間內罹患「重大傷病」，本契約自始無效，保險公司僅退還已繳保險費且不給付重大傷病保險金。然而，若「重大傷病」係因意外傷害事故所致，則不受等待期間限制，可申領重大傷病保險金。由於問題中未提及慢性腎衰竭是否因意外傷害事故所致，根據條文，若非因意外傷害事故，則無法申領重大傷病保險金。  
+條文依據：  
+- [第十二條 重大傷病保險金的給付]  
+- [第三十條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第三十條 不保事項</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J222" s="5" t="n"/>
+      <c r="K222" s="5" t="n"/>
+      <c r="L222" s="5" t="n"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:27</t>
+        </is>
+      </c>
+      <c r="N222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配重大傷病後，若在契約生效後80天罹患第一期乳癌，會拿到理賠金嗎?</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+不會拿到理賠金。根據條款，第一期乳癌屬於「需積極或長期治療之癌症」範圍，等待期間為契約生效日起持續有效九十日。若被保險人在等待期間內罹患重大傷病，契約自始無效，本公司僅退還已繳保險費且不計利息。
+條文依據：  
+- [第二條 名詞定義]  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>附表一：全民健康保險重大傷病項目 | 第十一條 重大傷病保險金的給付 | 第十五條 不保事項 | 第二條 名詞定義 | other_metadata</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr"/>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J223" s="5" t="n"/>
+      <c r="K223" s="5" t="n"/>
+      <c r="L223" s="5" t="n"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:29</t>
+        </is>
+      </c>
+      <c r="N223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>要保人想要終止國泰人壽自由配CFE契約，能否退保費?</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要保人可以終止契約，並退還未到期保險費。本公司會從已繳保險費中扣除按短期費率計算的已經過期間保險費後，將未到期保險費無息退還給要保人。
+條文依據：  
+- [第九條 契約的終止（一）]</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>第九條 契約的終止（一） | 第十五條 不保事項 | 第五條 契約有效期間及保證續保 | 第七條 本契約效力的恢復 | 第六條 續保保險費的交付、寬限期間及契約效力的停止 | 附表二：短期費率表</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr"/>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J224" s="5" t="n"/>
+      <c r="K224" s="5" t="n"/>
+      <c r="L224" s="5" t="n"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:31</t>
+        </is>
+      </c>
+      <c r="N224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>投保國泰人壽自由配CFE，若在等待期間內罹患重大傷病，要如何給付?</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，若被保險人在等待期間內罹患「重大傷病」，本契約自始無效，本公司僅無息退還已繳保險費予要保人。然而，若「重大傷病」係因意外傷害事故所致，則不受等待期間限制，本公司仍按約定給付「重大傷病保險金」。  
+條文依據：  
+- [第十一條 重大傷病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | 附表一：全民健康保險重大傷病項目 | 第十五條 不保事項 | 第十四條 除外責任 | payout_items</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr"/>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J225" s="5" t="n"/>
+      <c r="K225" s="5" t="n"/>
+      <c r="L225" s="5" t="n"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:34</t>
+        </is>
+      </c>
+      <c r="N225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CFE</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>投保自由配一年定期初次罹患重大傷病健康保險後，於第三年罹患先天性肌肉萎縮症，可以申領重大傷病保險金嗎？</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+一般情況下，若被保險人在保險有效期間內初次診斷罹患重大傷病，且符合「重大傷病」範圍並取得相關證明文件，可申領重大傷病保險金。然而，根據第十五條「不保事項」，若被保險人於投保前已符合重大傷病項目（如先天性疾病），則本契約自始無效，保險公司僅退還已繳保險費。因此，若先天性肌肉萎縮症屬於投保前已存在的重大傷病項目，則無法申領重大傷病保險金。
+條文依據：  
+- [第十一條 重大傷病保險金的給付]  
+- [第十五條 不保事項]</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 重大傷病保險金的給付 | other_metadata | 附表一：全民健康保險重大傷病項目 | 第十三條 重大傷病保險金的申領 | 第十五條 不保事項</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J226" s="5" t="n"/>
+      <c r="K226" s="5" t="n"/>
+      <c r="L226" s="5" t="n"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:37</t>
+        </is>
+      </c>
+      <c r="N226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>自由配重大疾病(甲型)保障的重大疾病有哪些疾病?</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+自由配重大疾病(甲型)保障的重大疾病包括以下疾病：  
+1. 腦中風後障礙(重度)  
+2. 癱瘓(重度)  
+3. 癌症(重度)  
+4. 急性心肌梗塞(重度)  
+5. 冠狀動脈繞道手術  
+6. 末期腎病變  
+7. 重大器官移植或造血幹細胞移植  
+條文依據：  
+- [第二條 名詞定義]</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>國泰人壽自由配一年定期初次罹患重大疾病健康保險(甲型)年繳費率表 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J227" s="5" t="n"/>
+      <c r="K227" s="5" t="n"/>
+      <c r="L227" s="5" t="n"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:40</t>
+        </is>
+      </c>
+      <c r="N227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>被保險人領了2次癌症(重度)追蹤照護金後身故，是否還有尚未給付的保險金供受益人領取?</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人已領取2次「癌症(重度)追蹤照護保險金」後身故，受益人無法再申領尚未給付的「癌症(重度)追蹤照護保險金」，因該保險金的給付條件為被保險人於保險單週年日仍生存者，且最多給付五年。被保險人身故後，該給付條件已不成立，因此不再給付。
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第二十三條 癌症保險金或罹癌基因檢測服務的申領</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J228" s="5" t="n"/>
+      <c r="K228" s="5" t="n"/>
+      <c r="L228" s="5" t="n"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:43</t>
+        </is>
+      </c>
+      <c r="N228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>保險金額2萬元，「罹癌基因檢測服務」費用8萬元，還會給付多少「癌症(重度)追蹤照護保險金」？</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若「罹癌基因檢測服務額度」低於附件一所列「罹癌基因檢測服務」之服務費用，被保險人僅得申領「癌症(重度)追蹤照護保險金」。因此，若服務費用為新臺幣8萬元，超過附件一所列補償金額新臺幣1,000元，被保險人無法申領「罹癌基因檢測服務」，僅能申領「癌症(重度)追蹤照護保險金」。依條文規定，「癌症(重度)追蹤照護保險金」按保險金額的十二倍計算，保險金額為新臺幣2萬元，則給付金額為新臺幣24萬元。  
+條文依據：  
+- [第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)]  
+- [附件一：罹癌基因檢測服務之項目、服務費用及補償金額表]</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 附件一：罹癌基因檢測服務之項目、服務費用及補償金額表 | 第二十三條 癌症保險金或罹癌基因檢測服務的申領 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | payout_items</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J229" s="5" t="n"/>
+      <c r="K229" s="5" t="n"/>
+      <c r="L229" s="5" t="n"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:46</t>
+        </is>
+      </c>
+      <c r="N229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>投保後1個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後1個月罹患重度癌症，因診斷確定日屬於第一保險單年度內，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「年繳應繳保險費」的一點零六倍。契約仍會持續有效，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J230" s="5" t="n"/>
+      <c r="K230" s="5" t="n"/>
+      <c r="L230" s="5" t="n"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:49</t>
+        </is>
+      </c>
+      <c r="N230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>投保後10個月罹患重度癌症，會給付哪些保險金？契約還會持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於投保後10個月（即第二保險單年度內）診斷確定罹患重度癌症，符合「初次診斷確定罹患癌症(重度)」的條件，本公司將給付「初次罹患癌症(重度)保險金」，金額為「保險金額」的十二倍。此外，契約仍會持續有效，並豁免續期保險費，但當期已繳付之未到期保險費不予退還。  
+條文依據：  
+- [第十三條 初次罹患癌症(重度)保險金的給付]  
+- [第十六條 癌症(重度)豁免保險費(第二保險單年度起適用)]</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 癌症(重度)豁免保險費(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用) | 第十條 契約的終止（二） | 第十三條 初次罹患癌症(重度)保險金的給付 | 第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J231" s="5" t="n"/>
+      <c r="K231" s="5" t="n"/>
+      <c r="L231" s="5" t="n"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:53</t>
+        </is>
+      </c>
+      <c r="N231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>DPA</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>投保醫心康愛，罹患肺癌一期，可領什麼保險金？</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+罹患肺癌一期屬於「癌症(初期)或癌症(輕度)」，可申領「初次罹患癌症(初期)或癌症(輕度)保險金」。若診斷確定日是在第一保險單年度內，可領「年繳應繳保險費」的一點零六倍；若診斷確定日是在第二保險單年度(含)以後，可領「保險金額」的五倍。此保險金最多僅給付一次。
+條文依據：  
+- [第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 初次罹患癌症(初期)或癌症(輕度)保險金的給付 | 第十三條 初次罹患癌症(重度)保險金的給付 | payout_items | 第十五條 癌症(重度)標靶藥物治療輔助保險金的給付(第二保險單年度起適用) | 第十四條 癌症(重度)追蹤照護保險金的給付或罹癌基因檢測服務的提供(第二保險單年度起適用)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J232" s="5" t="n"/>
+      <c r="K232" s="5" t="n"/>
+      <c r="L232" s="5" t="n"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:50:57</t>
+        </is>
+      </c>
+      <c r="N232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>若被保險人身故有何給付?</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人身故時，若本附約保險金尚未給付或未完全給付，則以被保險人之法定繼承人為該部分保險金之受益人，並依民法繼承編的相關規定分配受益順序及比例。
+條文依據：  
+- [第二十條 受益人]</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>第二十條 受益人 | 第十二條 重大疾病保險金的給付 | 第十一條 輕度重大疾病保險金的給付 | 第十四條 保險事故的通知與保險金的申請時間 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J233" s="5" t="n"/>
+      <c r="K233" s="5" t="n"/>
+      <c r="L233" s="5" t="n"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:00</t>
+        </is>
+      </c>
+      <c r="N233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>投保鍾溢祝福後，請問在第二年經醫院醫師初次診斷罹患「輕度重大疾病」中的癌症(輕度)者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+可以領到輕度重大疾病保險金，保險金額的百分之二十。根據條款，診斷確定日若在續保年度，輕度重大疾病保險金的給付比例為保險金額的百分之二十。此外，等待期間屆滿後即可申請，癌症（輕度）等待期間為九十日。
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [國泰人壽鍾溢祝福重大疾病健康保險附約（乙型）（外溢型）]</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | other_metadata | payout_items | 國泰人壽鍾溢祝福重大疾病健康保險附約(乙型) (外溢型)年繳費率表</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J234" s="5" t="n"/>
+      <c r="K234" s="5" t="n"/>
+      <c r="L234" s="5" t="n"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:02</t>
+        </is>
+      </c>
+      <c r="N234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+在投保後的第三年初次診斷罹患「重大疾病」者，可以領到重大疾病保險金，保險金額為保險金額的一點三倍。後續在第四年初次診斷罹患「輕度重大疾病」者，因已申領過重大疾病保險金，依條款規定無法再申領輕度重大疾病保險金。
+條文依據：  
+- [第十二條 重大疾病保險金的給付]  
+- [第十一條 輕度重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J235" s="5" t="n"/>
+      <c r="K235" s="5" t="n"/>
+      <c r="L235" s="5" t="n"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:06</t>
+        </is>
+      </c>
+      <c r="N235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>請問如果在投保後的第三年經醫院醫師初次診斷罹患「輕度重大疾病」者，可以領到重大疾病保險金嗎?可以領到保險金額的百分之多少?那後續又在第四年經醫院醫師初次診斷罹患「重大疾病」者，可以領到輕度重大疾病保險金嗎?可以領到保險金額的百分之多少?</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+1. 在投保後的第三年初次診斷罹患「輕度重大疾病」者，可以領到「輕度重大疾病保險金」，保險金額的百分之二十。  
+2. 在第四年初次診斷罹患「重大疾病」者，因已申領過「輕度重大疾病保險金」，依第十二條規定，重大疾病保險金需扣除已領取的輕度重大疾病保險金，最終可領到保險金額的一點三倍減去百分之二十。  
+條文依據：  
+- [第十一條 輕度重大疾病保險金的給付]  
+- [第十二條 重大疾病保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>第十一條 輕度重大疾病保險金的給付 | 第十二條 重大疾病保險金的給付 | 第十六條 除外責任 | payout_items | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J236" s="5" t="n"/>
+      <c r="K236" s="5" t="n"/>
+      <c r="L236" s="5" t="n"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:08</t>
+        </is>
+      </c>
+      <c r="N236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PX5</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>請問主約效力終止(因身故以外情形)，PX5還能持續有效嗎？</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+主約效力因身故以外的情形終止時，PX5附約效力可持續至附約當期已繳保險費期滿即行終止。  
+條文依據：  
+- [第十條 附約的終止（二）]</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>第十條 附約的終止（二） | 第七條 保險費的墊繳、附約的停效及復效 | 第五條 附約的保險期間及保證續保 | 第十三條 健康促進保險費折減 | 第九條 附約的終止（一）</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J237" s="5" t="n"/>
+      <c r="K237" s="5" t="n"/>
+      <c r="L237" s="5" t="n"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:09</t>
+        </is>
+      </c>
+      <c r="N237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>請問如果於「無理賠紀錄期間」屆滿日以內罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內罹患特定傷病，保險公司將給付「特定傷病保險金」，金額為「保險金額」加上「年繳應繳保險費總額」乘以1.02的加總。這筆保險金的受益人為被保險人本人，保險公司不受理其指定及變更。
+條文依據：  
+- [第十一條 特定傷病保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J238" s="5" t="n"/>
+      <c r="K238" s="5" t="n"/>
+      <c r="L238" s="5" t="n"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:11</t>
+        </is>
+      </c>
+      <c r="N238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為同一人，被保險人於「無理賠紀錄期間」屆滿日以內身故，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若要保人與被保險人為同一人，且被保險人於「無理賠紀錄期間」屆滿日以內身故，符合第十二條的條件，本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以一點零二。這筆保險金將依契約約定給付予受益人。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J239" s="5" t="n"/>
+      <c r="K239" s="5" t="n"/>
+      <c r="L239" s="5" t="n"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:14</t>
+        </is>
+      </c>
+      <c r="N239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>請問如果要保人與被保險人為不同人，被保險人於「無理賠紀錄期間」屆滿日以內生存，且被保險人未罹患特定傷病，會給付多少錢?這筆錢會給付給誰?</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於「無理賠紀錄期間」屆滿日以內生存，且未罹患特定傷病，則本公司將給付「無理賠關懷保險金」，金額為「年繳應繳保險費總額」乘以1.02。此筆保險金的受益人為要保人本人，本公司不受理其指定及變更。
+條文依據：  
+- [第十二條 無理賠關懷保險金的給付]  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第十二條 無理賠關懷保險金的給付 | 第十一條 特定傷病保險金的給付 | payout_items | 第二十七條 受益人的指定及變更</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J240" s="5" t="n"/>
+      <c r="K240" s="5" t="n"/>
+      <c r="L240" s="5" t="n"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:16</t>
+        </is>
+      </c>
+      <c r="N240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，會給保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶若於本契約有效期間內身故，保險公司會依約定給付保險金。若保戶在「無理賠紀錄期間」內身故，亦符合保險金給付條件。此外，若受益人在分期定期保險金給付期間內死亡，尚未領取的分期定期保險金將一次貼現給付予受益人之法定繼承人。  
+條文依據：  
+- [第五條 保險範圍]  
+- [第二十八條 本契約受益人死亡或失蹤的處理]</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第十七條 除外責任（二） | 第二十三條 受益人受益權之喪失 | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr"/>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J241" s="5" t="n"/>
+      <c r="K241" s="5" t="n"/>
+      <c r="L241" s="5" t="n"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:19</t>
+        </is>
+      </c>
+      <c r="N241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>保戶如果身故，身故申領的保險金會給誰?</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶身故後，身故保險金的受益人依以下情況處理：  
+1. 若特定傷病保險金尚未給付或未完全給付，則以被保險人之法定繼承人為受益人。  
+2. 若無理賠關懷保險金受益人同時或先於被保險人身故，則以被保險人為該項保險金受益人；若被保險人已身故，則以被保險人之法定繼承人為受益人。  
+3. 當受益人為法定繼承人時，其受益順序及應得比例適用民法繼承編相關規定。
+條文依據：  
+- [第二十七條 受益人的指定及變更]</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>第五條 保險範圍 | 第二十三條 受益人受益權之喪失 | 第二十七條 受益人的指定及變更 | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr"/>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J242" s="5" t="n"/>
+      <c r="K242" s="5" t="n"/>
+      <c r="L242" s="5" t="n"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:22</t>
+        </is>
+      </c>
+      <c r="N242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>如果保戶投保繳費年期20年的滿溢寶，然後在第20保單年度身故的話，可以領到多少錢?</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+根據條款，若受益人在分期定期保險金給付期間內死亡，尚未領取的分期定期保險金將以第二條定義之分期定期保險金預定利率計算，一次貼現給付予受益人的法定繼承人。至於具體金額，需依保險金額及分期定期保險金的計算方式確定，條款未提供具體金額計算公式或範例。
+條文依據：  
+- [第二十八條 本契約受益人死亡或失蹤的處理]</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>other_metadata | 第二十八條 本契約受益人死亡或失蹤的處理 | 第二十六條 投保年齡的計算及錯誤的處理 | 第十一條 特定傷病保險金的給付 | 第二十二條 分期定期保險金給付申領文件、給付期限及未依限給付之效果</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr"/>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J243" s="5" t="n"/>
+      <c r="K243" s="5" t="n"/>
+      <c r="L243" s="5" t="n"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:24</t>
+        </is>
+      </c>
+      <c r="N243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>FSAFSB</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之滿溢寶特定傷病定期健康保險（定期給付型）（外溢型）100萬元，年繳應繳保險費為83,500元，年繳實繳保險費為78,490元。若被保險人於第二保險單年度自殺身故，則無理賠關懷保險金可以領到多少錢？</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人於第二保險單年度自殺身故，根據第十七條除外責任（二），一般情況下自殺屬於除外責任，本公司不負給付無理賠關懷保險金的責任。然而，條文中明確規定「自契約訂立或復效之日起二年後故意自殺致死者，本公司仍負給付第十二條保險金之責任」。因此，若自殺發生於契約訂立或復效日起未滿二年，無理賠關懷保險金無法領取；若已滿二年，則可依第十二條計算給付金額。
+條文依據：  
+- [第十七條 除外責任（二）]  
+- [第十二條 無理賠關懷保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 無理賠關懷保險金的給付 | 第十七條 除外責任（二） | 第十一條 特定傷病保險金的給付 | other_metadata | 第十九條 失蹤處理</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J244" s="5" t="n"/>
+      <c r="K244" s="5" t="n"/>
+      <c r="L244" s="5" t="n"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:27</t>
+        </is>
+      </c>
+      <c r="N244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>請問如果第2保單年度罹患特定傷病，可以給付多少錢?給付給誰?未來還有其他保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+若被保險人在第二保險單年度（含）以後罹患特定傷病，依條款規定，本公司將給付以下保險金：  
+1. **特定傷病保險金**：給付金額為保險金額，且僅給付一次。  
+2. **生活補助保險金**：自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢保險單週年日仍生存者，按保險金額的36%給付，最高給付次數為十次。  
+給付對象為被保險人。  
+條文依據：  
+- [第十二條 特定傷病保險金的給付]  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>第十二條 特定傷病保險金的給付 | 第五條 保險範圍 | 第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第二條 名詞定義 | 第十五條 保險費豁免（第二保險單年度起適用）</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J245" s="5" t="n"/>
+      <c r="K245" s="5" t="n"/>
+      <c r="L245" s="5" t="n"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:29</t>
+        </is>
+      </c>
+      <c r="N245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>請問我115年1月1日投保，怎麼得到健康促進保險費折減?</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+要獲得健康促進保險費折減，您需完成以下步驟：  
+1. 使用保險公司指定的程式並加入指定的健康計劃。  
+2. 完成程式註冊程序，執行該程式並授權保險公司取得與健康促進相關的電子紀錄。  
+3. 保險公司將根據成功傳輸的電子紀錄，依其訂定的辦法計算您的會員等級。  
+4. 若於「指定日期」您的會員等級符合標準，則次一保險單年度的保險費可按表列比例折減：  
+   - 實踐家：折減3%  
+   - 樂享家或高於樂享家的會員等級：折減10%  
+注意：復效或豁免的保險費不適用折減約定。
+條文依據：  
+- [第十六條 健康促進保險費折減]</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>第十六條 健康促進保險費折減 | 第二十三條 投保年齡的計算及錯誤的處理 | 第十五條 保險費豁免（第二保險單年度起適用） | 第五條 保險範圍 | payout_items</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J246" s="5" t="n"/>
+      <c r="K246" s="5" t="n"/>
+      <c r="L246" s="5" t="n"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:32</t>
+        </is>
+      </c>
+      <c r="N246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，在什麼時候可以領取生活補助保險金?</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在114/1/10投保後，等待期間為30日，因此保險契約的有效期間自114/2/9開始計算。根據條款，生活補助保險金的給付需符合以下條件：  
+1. 被保險人於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病。  
+2. 自初次診斷確定罹患特定傷病的次一個保險單週年日起，每逢各保險單週年日仍生存者，給付生活補助保險金。  
+保戶於115/3/30罹患特定傷病，符合第二保險單年度的條件（第二保險單年度自115/1/10起算）。因此，生活補助保險金的首次給付時間為初次診斷確定罹患特定傷病的次一個保險單週年日，即116/1/10，並於每逢保險單週年日仍生存時繼續給付。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | other_metadata | 第十一條 契約的終止（三） | payout_items | 第十二條 特定傷病保險金的給付</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J247" s="5" t="n"/>
+      <c r="K247" s="5" t="n"/>
+      <c r="L247" s="5" t="n"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:36</t>
+        </is>
+      </c>
+      <c r="N247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>保戶在114/1/10投保樂鍾溢，如果他在115/3/30罹患特定傷病的話，他在115/1/9會領到無理賠回饋保險金嗎?</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+保戶在115/1/9無法領取無理賠回饋保險金。根據條款，無理賠回饋保險金的給付條件包括「未曾因罹患特定傷病申領特定傷病保險金」且「每逢保險單年度末仍生存」。保戶於114/1/10投保，保險單年度末為每年的1月9日。由於保戶在115/3/30罹患特定傷病並申領特定傷病保險金，這不符合「未曾申領特定傷病保險金」的條件，因此無法領取115/1/9的無理賠回饋保險金。
+條文依據：  
+- 第十四條 無理賠回饋保險金的給付</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>payout_items | 第十四條 無理賠回饋保險金的給付 | other_metadata | 第十二條 特定傷病保險金的給付 | 第二十條 無理賠回饋保險金的申領</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J248" s="5" t="n"/>
+      <c r="K248" s="5" t="n"/>
+      <c r="L248" s="5" t="n"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:39</t>
+        </is>
+      </c>
+      <c r="N248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>被保險人於第一保險單年度罹患急性心肌梗塞（重度），生活補助保險金最多可以領取幾次？</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+被保險人於第一保險單年度罹患急性心肌梗塞（重度），無法領取生活補助保險金。根據條款規定，生活補助保險金的給付僅適用於第二保險單年度（含）以後的有效期間內初次診斷確定罹患特定傷病的情形。
+條文依據：  
+- [第十三條 生活補助保險金的給付（第二保險單年度起適用）]</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>第十三條 生活補助保險金的給付（第二保險單年度起適用） | 第十二條 特定傷病保險金的給付 | 第十一條 契約的終止（三） | 第五條 保險範圍 | 第二條 名詞定義</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr"/>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr"/>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J249" s="5" t="n"/>
+      <c r="K249" s="5" t="n"/>
+      <c r="L249" s="5" t="n"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:40</t>
+        </is>
+      </c>
+      <c r="N249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>被保險人為60歲女性，投保繳費期間20年期之樂鍾心特定傷病定期健康保險（外溢型）5單位，每單位年繳應繳保險費為1675元，則每逢保險單年度末生存者，可以領取多少無理賠關懷保險金？</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>回答：  
+每逢保險單年度末生存者，若符合條件，可以領取的「無理賠回饋保險金」金額為：每單位年繳應繳保險費的百分之十乘以單位數。計算如下：  
+每單位年繳應繳保險費為1675元，百分之十為167.5元（元以下無條件進位為168元）。  
+投保5單位，則168元 × 5單位 = 840元。  
+因此，每逢保險單年度末生存者，可以領取840元的「無理賠回饋保險金」。  
+條文依據：  
+- [第十四條 無理賠回饋保險金的給付]</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>第十四條 無理賠回饋保險金的給付 | other_metadata | payout_items | 第二十條 無理賠回饋保險金的申領 | 第十二條 特定傷病保險金的給付</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J250" s="5" t="n"/>
+      <c r="K250" s="5" t="n"/>
+      <c r="L250" s="5" t="n"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:51:52</t>
+        </is>
+      </c>
+      <c r="N250" s="5" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
